--- a/Erettsegi_Adatok/Irodalom/Összes mű.xlsx
+++ b/Erettsegi_Adatok/Irodalom/Összes mű.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programozás\Gyakorlás\Web\Erettsegi-v2\Erettsegi_Adatok\Irodalom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85EFC18-525B-49E0-AD4A-7A610F63F0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878EBC9C-A43C-45C0-9818-FFC7AB1CB940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-825" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Műfaj</t>
   </si>
@@ -130,6 +130,21 @@
   </si>
   <si>
     <t>(1292-95)</t>
+  </si>
+  <si>
+    <t>Jacopone da Todi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Himnusz a fájdalmas anyáról </t>
+  </si>
+  <si>
+    <t>planctus (siralom)</t>
+  </si>
+  <si>
+    <t>Anonymus</t>
+  </si>
+  <si>
+    <t>Gesta Hungarorum</t>
   </si>
 </sst>
 </file>
@@ -447,11 +462,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="120" bestFit="1" customWidth="1"/>
@@ -601,6 +616,25 @@
         <v>33</v>
       </c>
     </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Erettsegi_Adatok/Irodalom/Összes mű.xlsx
+++ b/Erettsegi_Adatok/Irodalom/Összes mű.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programozás\Gyakorlás\Web\Erettsegi-v2\Erettsegi_Adatok\Irodalom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878EBC9C-A43C-45C0-9818-FFC7AB1CB940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DAD1FF-AC74-4E39-BAA0-DE13A2A6F5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="241">
   <si>
     <t>Műfaj</t>
   </si>
@@ -129,35 +129,687 @@
     <t>Halotti beszéd és könyörgés</t>
   </si>
   <si>
-    <t>(1292-95)</t>
-  </si>
-  <si>
     <t>Jacopone da Todi</t>
   </si>
   <si>
-    <t xml:space="preserve">Himnusz a fájdalmas anyáról </t>
-  </si>
-  <si>
-    <t>planctus (siralom)</t>
-  </si>
-  <si>
-    <t>Anonymus</t>
-  </si>
-  <si>
     <t>Gesta Hungarorum</t>
+  </si>
+  <si>
+    <t>Ismeretlen szerző</t>
+  </si>
+  <si>
+    <t>Halotti prédikáció (beszéd) és könyörgés</t>
+  </si>
+  <si>
+    <t>Középkor (1192–1195 körül)</t>
+  </si>
+  <si>
+    <t>Az emberi mulandóság, a bűnbeesés miatti halandóság ecsetelése és könyörgés a halott lelki üdvéért.</t>
+  </si>
+  <si>
+    <t>Első összefüggő magyar nyelvű szövegemlékünk. Figura etymologica használata ("halálnak halálával halsz").</t>
+  </si>
+  <si>
+    <t>Anonymus (P. mester)</t>
+  </si>
+  <si>
+    <t>Geszta (udvari epika)</t>
+  </si>
+  <si>
+    <t>Középkor (1200 körül / 13. sz. eleje)</t>
+  </si>
+  <si>
+    <t>A magyar honfoglalás története, a vezérek tettei és a honfoglaló nemzetségek származásának leírása.</t>
+  </si>
+  <si>
+    <t>Célja a honfoglalás jogosságának és az uralkodóház dicsőségének igazolása. Mondai elemeket (pl. Emese álma) is tartalmaz.</t>
+  </si>
+  <si>
+    <t>Himnusz, planctus (siralom)</t>
+  </si>
+  <si>
+    <t>Középkor (13. sz. vége)</t>
+  </si>
+  <si>
+    <t>Ómagyar Mária-siralom</t>
+  </si>
+  <si>
+    <t>Planctus (siralom), Mária-siralom</t>
+  </si>
+  <si>
+    <t>Középkor (1300 körül)</t>
+  </si>
+  <si>
+    <t>Mária egyes szám első személyben panaszolja el fájdalmát fia kínzása és halála miatt.</t>
+  </si>
+  <si>
+    <t>Az első fennmaradt magyar nyelvű vers. Dramatikus felépítés, tiszta rímek és mély érzelmi átfűtöttség jellemzi.</t>
+  </si>
+  <si>
+    <t>Himnusz a fájdalmas anyáról (Stabat Mater)</t>
+  </si>
+  <si>
+    <t>A kereszt alatt álló, fiát gyászoló Szűz Mária szenvedésének leírása, és a hívő vágya arra, hogy osztozzon ebben a fájdalomban.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A középkori vallásos líra csúcsa. Fő motívuma a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compassio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (együttérzés). Tárgyszerű leírásból halad a mély, szubjektív azonosulás és a megváltásért való könyörgés felé. Az Ómagyar Mária-siralom európai párhuzama.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ismeretlen (francia)</t>
+  </si>
+  <si>
+    <t>Roland-ének</t>
+  </si>
+  <si>
+    <t>Lovageposz</t>
+  </si>
+  <si>
+    <t>Középkor (11. sz. vége)</t>
+  </si>
+  <si>
+    <t>Nagy Károly seregének visszavonulásakor Roland lovag a hátvédet vezeti, és hősiesen feláldozza magát a túlerőben lévő mórokkal (és az áruló Ganelonnal) szemben.</t>
+  </si>
+  <si>
+    <t>A lovagi eszmény (hűbéri hűség, becsület, keresztény hit védelme) legtisztább irodalmi megfogalmazása.</t>
+  </si>
+  <si>
+    <t>Ismeretlen (német)</t>
+  </si>
+  <si>
+    <t>Nibelung-ének</t>
+  </si>
+  <si>
+    <t>Hőseposz, lovageposz</t>
+  </si>
+  <si>
+    <t>Középkor (13. sz. eleje)</t>
+  </si>
+  <si>
+    <t>A sebezhetetlen Siegfried meggyilkolása és özvegyének, Krimhildának pusztító, vérfürdőbe torkolló bosszúja.</t>
+  </si>
+  <si>
+    <t>A germán mitológia (pogány, barbár szenvedélyek) és a keresztény-lovagi erények érdekes keveredése.</t>
+  </si>
+  <si>
+    <t>Ismeretlen (kelta/francia)</t>
+  </si>
+  <si>
+    <t>Trisztán és Izolda</t>
+  </si>
+  <si>
+    <t>Lovagregény (verses)</t>
+  </si>
+  <si>
+    <t>Középkor (12. század)</t>
+  </si>
+  <si>
+    <t>Egy varázsital hatására Trisztán lovag és nagybátyjának (Márk királynak) felesége, Izolda halálosan és elszakíthatatlanul egymásba szeretnek.</t>
+  </si>
+  <si>
+    <t>A végzetes, mindent elsöprő szerelem toposza. A lovagi hűség (a királyhoz) és a személyes érzelmek tragikus konfliktusa.</t>
+  </si>
+  <si>
+    <t>Walther von der Vogelweide</t>
+  </si>
+  <si>
+    <t>A hársfaágak csendes árnyán (Unter der linden)</t>
+  </si>
+  <si>
+    <t>Lovagi líra (minnesang), helyzetdal</t>
+  </si>
+  <si>
+    <t>Középkor (1200 körül)</t>
+  </si>
+  <si>
+    <t>Egy fiatal (vélhetően alacsonyabb rangú) lány boldogan és titokzatosan emlékszik vissza egy lovaggal történt szerelmi találkájára a természetben.</t>
+  </si>
+  <si>
+    <t>Szakít a hagyományos trubadúrlírával (ahol a nő egy elérhetetlen, hideg úrnő): itt a szerelem beteljesül, őszinte, és a nő szemszögéből szólal meg. A természet és a szerelem teljes harmóniája jelenik meg.</t>
+  </si>
+  <si>
+    <t>Ismeretlen (vándordiákok)</t>
+  </si>
+  <si>
+    <t>Carmina Burana</t>
+  </si>
+  <si>
+    <t>Versgyűjtemény (bordalok, szerelmes versek)</t>
+  </si>
+  <si>
+    <t>Középkor (12-13. század)</t>
+  </si>
+  <si>
+    <t>A vágáns diákok életörömet, szerelmet, bort dicsőítő, és az egyházi álszentséget ostorozó verseinek gyűjteménye.</t>
+  </si>
+  <si>
+    <t>A korabeli hivatalos aszketikus (testet sanyargató) egyházi világképpel szemben az evilági boldogságot hirdeti.</t>
+  </si>
+  <si>
+    <t>François Villon</t>
+  </si>
+  <si>
+    <t>A Nagy Testamentum</t>
+  </si>
+  <si>
+    <t>Lírai önéletrajz (végrendelet)</t>
+  </si>
+  <si>
+    <t>Középkor vége / Reneszánsz hajnala (1461)</t>
+  </si>
+  <si>
+    <t>A halálra készülő, bűnbánó költő ironikus és őszinte formában hagyja "vagyonát" (verseit és gúnyos megjegyzéseit) az ismerőseire.</t>
+  </si>
+  <si>
+    <t>A középkori haláltudat (danse macabre) és a reneszánsz öntudat keveredik benne. Új balladaforma megalkotója.</t>
+  </si>
+  <si>
+    <t>Dante Alighieri</t>
+  </si>
+  <si>
+    <t>Isteni színjáték</t>
+  </si>
+  <si>
+    <t>Drámai költemény (Eposz)</t>
+  </si>
+  <si>
+    <t>Középkor / Kora reneszánsz (1307–1320)</t>
+  </si>
+  <si>
+    <t>A költő céltalanná vált élete miatt 1300 nagycsütörtökén túlvilági utazásra indul a Pokol, Purgatórium és Paradicsom birodalmába, Vergilius és Beatrice vezetésével.</t>
+  </si>
+  <si>
+    <t>A "középkor enciklopédiája". Szigorú hármas szerkezetre épül (3 könyv, 33 ének, 3 soros tercinák), mely a Szentháromságot szimbolizálja., gazdag szimbolika, és a bűnök/erények pontos hierarchiája jellemzi.</t>
+  </si>
+  <si>
+    <t>Ismeretlen (több szerző)</t>
+  </si>
+  <si>
+    <t>Biblia (Ószövetség, Teremtés könyve)</t>
+  </si>
+  <si>
+    <t>Szent irat, mítoszok, mondák gyűjteménye</t>
+  </si>
+  <si>
+    <t>Ókor (Kr. e. 12. sz. – Kr. e. 2. sz.)</t>
+  </si>
+  <si>
+    <t>A világ és az ember teremtése, a bűnbeesés története, valamint a zsidó nép ősatyáinak (Ábrahám, Izsák, Jákob, József) kiválasztása és szövetsége Istennel.</t>
+  </si>
+  <si>
+    <t>Thomas Mann</t>
+  </si>
+  <si>
+    <t>József és testvérei</t>
+  </si>
+  <si>
+    <t>Regénytetralógia (Mítoszregény)</t>
+  </si>
+  <si>
+    <t>20. század (1933–1943)</t>
+  </si>
+  <si>
+    <t>A bibliai József-történet hatalmas, lélektani és mitológiai mélységű újramesélése, amely végigköveti József útját a kútba dobástól az egyiptomi felemelkedésig.</t>
+  </si>
+  <si>
+    <t>Francesco Petrarca</t>
+  </si>
+  <si>
+    <t>Dalos könyv (Canzoniere)</t>
+  </si>
+  <si>
+    <t>Versciklus (dalok, szonettek)</t>
+  </si>
+  <si>
+    <t>Reneszánsz (14. század közepe)</t>
+  </si>
+  <si>
+    <t>A költő Laura iránti reménytelen, epekedő szerelmét, majd a nő halála utáni fájdalmát énekli meg 366 versben.</t>
+  </si>
+  <si>
+    <t>A reneszánsz ember önismeretének megjelenése. A petrarcai szonettforma (abba abba cdc dcd) megteremtése. A szerelem mint földi, ambivalens érzelem ábrázolása.</t>
+  </si>
+  <si>
+    <t>Janus Pannonius</t>
+  </si>
+  <si>
+    <t>Pannónia dicsérete</t>
+  </si>
+  <si>
+    <t>Epigramma</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1465)</t>
+  </si>
+  <si>
+    <t>A költő büszkén hirdeti, hogy bár eddig Itália volt a kultúra központja, az ő költészete révén szülőföldje, Pannónia is dicsőséget szerzett.</t>
+  </si>
+  <si>
+    <t>Megjelenik benne a tipikus humanista írói öntudat és a hírnév, dicsőség iránti vágy.</t>
+  </si>
+  <si>
+    <t>Egy dunántúli mandulafáról</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1466)</t>
+  </si>
+  <si>
+    <t>Egy zord télben, fagyban is virágot bontó mandulafa dacol a természettel, de sorsa a biztos fagyhalál.</t>
+  </si>
+  <si>
+    <t>A mandulafa a költő allegóriája: a "szellemi hontalanság", a kulturálatlan magyar közegben meg nem értett humanista tudós tragédiája.</t>
+  </si>
+  <si>
+    <t>Giovanni Boccaccio</t>
+  </si>
+  <si>
+    <t>Dekameron</t>
+  </si>
+  <si>
+    <t>Novellagyűjtemény (Keretes elbeszélés)</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1348–1353)</t>
+  </si>
+  <si>
+    <t>A pestis elől vidékre menekülő 10 fiatal 10 nap alatt 100 történetet mesél el egymásnak szerelemről, okosságról, rászedésről.</t>
+  </si>
+  <si>
+    <t>A novella műfajának megteremtése. A középkori aszkézissel szemben a földi élet, a humor, és az emberi leleményesség (okosság) dicsérete.</t>
+  </si>
+  <si>
+    <t>Dekameron: A három gyűrű története</t>
+  </si>
+  <si>
+    <t>Novella (példázat)</t>
+  </si>
+  <si>
+    <t>Reneszánsz</t>
+  </si>
+  <si>
+    <t>Melkisédek, a zsidó uzsorás egy három azonos gyűrűről szóló mesével vágja ki magát a szultán csapdájából.</t>
+  </si>
+  <si>
+    <t>A reneszánsz vallási tolerancia és az emberi leleményesség (okosság) irodalmi példája.</t>
+  </si>
+  <si>
+    <t>Dekameron: Federigo és a sólyom</t>
+  </si>
+  <si>
+    <t>Novella</t>
+  </si>
+  <si>
+    <t>Federigo megsüti egyetlen kincsét, a sólymát, hogy megvendégelje szerelmét. Az asszony a nemes tett miatt hozzámegy.</t>
+  </si>
+  <si>
+    <t>A "sólyom-elmélet" alapműve. A lovagi (pénzszóró) és a reneszánsz (jellemalapú) értékrend ütközése.</t>
+  </si>
+  <si>
+    <t>Balassi Bálint</t>
+  </si>
+  <si>
+    <t>Borivóknak való</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1589 tavasza)</t>
+  </si>
+  <si>
+    <t>A tavasz szépségét, a természet megújulását és a végvári katonaélet vidám, gondtalan pillanatait ünnepli.</t>
+  </si>
+  <si>
+    <t>Antik hagyományok (bordal) és reneszánsz életöröm ötvözete. A természet harmóniája és a tavaszi újjászületés dominál.</t>
+  </si>
+  <si>
+    <t>Egy katonaének (In laudem confiniorum)</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1589)</t>
+  </si>
+  <si>
+    <t>A végvári vitézek mindennapjait, hősiességét, a harci kedvet és a katonaélet árnyoldalait (sebesülés, halál) mutatja be hitelesen.</t>
+  </si>
+  <si>
+    <t>3 pillérű (szimmetrikus, híd-szerkezetű) reneszánsz kompozíció. A katonaéletet a legmagasabb erkölcsi rangra (emberség, vitézség) emeli.</t>
+  </si>
+  <si>
+    <t>Hogy Júliára talála...</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1588)</t>
+  </si>
+  <si>
+    <t>A költő váratlanul megpillantja szerelmét, Júliát, akit ujjongva, boldogan köszönt, de a nő csak hideg, fenséges mosollyal válaszol az udvarlásra.</t>
+  </si>
+  <si>
+    <t>Petrarca hatása erősen érezhető. Fokozásos halmozás és virág-metaforák sora jellemzi ("szívem vidámsága"). A lovag-úrnő távolság klasszikus megjelenése.</t>
+  </si>
+  <si>
+    <t>Adj már csendességet</t>
+  </si>
+  <si>
+    <t>Istenes ének (Himnusz / Könyörgés)</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1591 k.)</t>
+  </si>
+  <si>
+    <t>A bűneivel küzdő, élete válságába jutott és lelki békét kereső ember kétségbeesett, majd megerősödő bizalommal teli könyörgése Istenhez.</t>
+  </si>
+  <si>
+    <t>Szimmetrikus szerkezet (2-4-2 versszak). Közvetlen, személyes istenviszony jelenik meg benne; egy drámai belső vita a megváltás lehetőségéről (hit és kétség kettőssége).</t>
+  </si>
+  <si>
+    <t>William Shakespeare</t>
+  </si>
+  <si>
+    <t>Rómeó és Júlia</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1595–1597 körül)</t>
+  </si>
+  <si>
+    <t>Két ellenséges veronai család (Montague és Capulet) gyermekeinek végzetes, titkos szerelme, amely a fiatalok halálával végül kibékíti a családokat.</t>
+  </si>
+  <si>
+    <t>A reneszánsz (szabad párválasztás, tiszta érzelmek) és a feudális középkori (családi viszály, vérbosszú) értékrend tragikus konfliktusa.</t>
+  </si>
+  <si>
+    <t>Óda</t>
+  </si>
+  <si>
+    <t>Dal / Óda</t>
+  </si>
+  <si>
+    <t>Bordal</t>
+  </si>
+  <si>
+    <t>Tragédia</t>
+  </si>
+  <si>
+    <t>Károli Gáspár</t>
+  </si>
+  <si>
+    <t>Vizsolyi Biblia</t>
+  </si>
+  <si>
+    <t>Bibliafordítás</t>
+  </si>
+  <si>
+    <t>Késő reneszánsz / Reformáció (1590)</t>
+  </si>
+  <si>
+    <t>A teljes Ó- és Újszövetség első hiánytalan magyar nyelvű fordítása.</t>
+  </si>
+  <si>
+    <t>A magyar nyelvű írásbeliség és vallásgyakorlás legfontosabb mérföldköve, a reformáció legnagyobb hazai vívmánya. Nyelvezete máig hatással van az irodalomra.</t>
+  </si>
+  <si>
+    <t>Szenci Molnár Albert</t>
+  </si>
+  <si>
+    <t>42. zsoltár (Zsoltáros könyv)</t>
+  </si>
+  <si>
+    <t>Zsoltárparafrázis</t>
+  </si>
+  <si>
+    <t>Késő reneszánsz / Reformáció (1607)</t>
+  </si>
+  <si>
+    <t>Az Isten közelségére és a hit megtartására szomjazó, ellenséges közegben gúnyolt hívő ember panaszos, majd megnyugvó fohásza.</t>
+  </si>
+  <si>
+    <t>Hűen követi a bibliai eredetit, de zeneileg és formailag is kiválóan alkalmazkodik a kor protestáns énekes hagyományaihoz. Dávid zsoltárainak verses átköltése.</t>
+  </si>
+  <si>
+    <t>Heltai Gáspár</t>
+  </si>
+  <si>
+    <t>Száz fabula</t>
+  </si>
+  <si>
+    <t>Fabula (állatmese)</t>
+  </si>
+  <si>
+    <t>Reneszánsz / Reformáció (1566)</t>
+  </si>
+  <si>
+    <t>Aiszóposz ókori állatmeséinek magyar nyelvű, erkölcsi tanulsággal ellátott feldolgozásai.</t>
+  </si>
+  <si>
+    <t>A mesék állatszereplői tipikus emberi gyarlóságokat testesítenek meg. A protestáns erkölcsi tanítás népszerű, szórakoztató eszköze volt.</t>
+  </si>
+  <si>
+    <t>Tinódi Lantos Sebestyén</t>
+  </si>
+  <si>
+    <t>Eger vár viadaljáról való ének</t>
+  </si>
+  <si>
+    <t>Históriás ének</t>
+  </si>
+  <si>
+    <t>Reneszánsz (1553)</t>
+  </si>
+  <si>
+    <t>Az 1552-es egri várvédők (Dobó István és katonái) hősies, törökök elleni győzelmét örökíti meg.</t>
+  </si>
+  <si>
+    <t>Fő funkciója a hiteles tájékoztatás és a harci kedv ébrentartása. Dísztelen, de tényszerű és részletes epikai alkotás, mely zenés kísérettel szólalt meg.</t>
+  </si>
+  <si>
+    <t>Gyergyai Albert</t>
+  </si>
+  <si>
+    <t>História egy Árgirus nevű királyfiról...</t>
+  </si>
+  <si>
+    <t>Széphistória (Verses mese)</t>
+  </si>
+  <si>
+    <t>Reneszánsz (16. század vége)</t>
+  </si>
+  <si>
+    <t>Árgirus királyfi és egy tündérlány kalandos, megpróbáltatásokkal és csodákkal teli szerelmi története.</t>
+  </si>
+  <si>
+    <t>A mesei konvenciók (csodák, 3-as szám, boszorkányok) mögött reneszánsz életszemlélet áll: a földi boldogság és a szerelem a legfőbb érték.</t>
+  </si>
+  <si>
+    <t>Zrínyi Miklós</t>
+  </si>
+  <si>
+    <t>Szigeti veszedelem</t>
+  </si>
+  <si>
+    <t>Barokk eposz</t>
+  </si>
+  <si>
+    <t>Barokk (1651, Bécs)</t>
+  </si>
+  <si>
+    <t>Az 1566-os szigetvári ostrom krónikája, ahol Zrínyi dédapja és maroknyi serege mártírhalált halt a sokszoros túlerőben lévő török sereggel és Szulejmánnal szemben.</t>
+  </si>
+  <si>
+    <t>Az Athleta Christi (Krisztus katonája) eszmény megfogalmazása. Barokk monumentalitás, tudatos szerkesztés (1566 versszak), eposzi kellékek bőséges használata. A történelmi vereséget erkölcsi győzelemmé emeli.</t>
+  </si>
+  <si>
+    <t>Mikes Kelemen</t>
+  </si>
+  <si>
+    <t>Törökországi levelek</t>
+  </si>
+  <si>
+    <t>Fiktív levél(gyűjtemény)</t>
+  </si>
+  <si>
+    <t>Késő barokk (1717-től)</t>
+  </si>
+  <si>
+    <t>A Rákóczi-szabadságharc bukása után a fejedelmet Rodostóba kísérő író fiktív "nagynénjének" írt levelei a bujdosók mindennapjairól, honvágyáról.</t>
+  </si>
+  <si>
+    <t>Megteremti a magyar prózai társalgási stílust (könnyed, anekdotázó, humoros). Az irodalmi levél műfajának magyarországi csúcspontja.</t>
+  </si>
+  <si>
+    <t>Rákóczi-nóta</t>
+  </si>
+  <si>
+    <t>Panaszdal / Történeti ének</t>
+  </si>
+  <si>
+    <t>Kuruc kor (18. század eleje)</t>
+  </si>
+  <si>
+    <t>A nemzet siralmas sorsát és a szabadságharc bukását panaszolja el. Kéri Istent, hogy oltalmazza meg a hazát az elnyomóktól (Habsburgoktól).</t>
+  </si>
+  <si>
+    <t>A kuruc közösségi költészet legemblematikusabb darabja. Pátoszos, könyörgő hangvétel jellemzi, dallama később a nemzeti zenei kultúra részévé vált.</t>
+  </si>
+  <si>
+    <t>Molière</t>
+  </si>
+  <si>
+    <t>Tartuffe</t>
+  </si>
+  <si>
+    <t>Komédia / Klasszicista dráma</t>
+  </si>
+  <si>
+    <t>Francia klasszicizmus (1664)</t>
+  </si>
+  <si>
+    <t>Orgon, a gazdag és hiszékeny polgár befogadja az álszent Tartuffe-öt, aki teljesen a befolyása alá vonja. Kis híján kiforgatja vagyonából és tönkreteszi a családot, míg a királyi hatalom közbe nem lép.</t>
+  </si>
+  <si>
+    <t>A vallási képmutatás (álszentség) és a vakhit éles kritikája. Tökéletesen érvényesül benne a hármas egység szabálya, a jellemkomikum és a helyzetkomikum, valamint a rezonőr szerepe (Cléante).</t>
+  </si>
+  <si>
+    <t>A fösvény</t>
+  </si>
+  <si>
+    <t>Komédia</t>
+  </si>
+  <si>
+    <t>Francia klasszicizmus (1668)</t>
+  </si>
+  <si>
+    <t>Az idősödő, özvegy Harpagon mindent a beteges pénzsóvárságának rendel alá. Imádott pénzesládájáért még gyermekei (Cléante és Élise) szerelmi boldogságát is hajlandó lenne feláldozni.</t>
+  </si>
+  <si>
+    <t>A jellemkomikum legtisztább példája az irodalomban, ahol a főhős egyetlen eltúlzott tulajdonsága (a kapzsiság) mozgatja a szálakat és teszi nevetségessé az alakját.</t>
+  </si>
+  <si>
+    <t>Daniel Defoe</t>
+  </si>
+  <si>
+    <t>Robinson Crusoe</t>
+  </si>
+  <si>
+    <t>Robinzonád (Kalandregény)</t>
+  </si>
+  <si>
+    <t>Angol felvilágosodás (1719)</t>
+  </si>
+  <si>
+    <t>Egy hajótörött lakatlan szigetre vetődik, ahol a civilizációtól elzárva a semmiből teremti újra a polgári életet, a gazdaságot és a társadalmi rendet.</t>
+  </si>
+  <si>
+    <t>A felvilágosodás optimizmusának regénye: az angol polgárság gyakorlatiasságának, a józan észnek és a szorgalmas munkának a diadala a természet felett.</t>
+  </si>
+  <si>
+    <t>Jonathan Swift</t>
+  </si>
+  <si>
+    <t>Gulliver utazásai</t>
+  </si>
+  <si>
+    <t>Szatirikus kalandregény</t>
+  </si>
+  <si>
+    <t>Angol felvilágosodás (1726)</t>
+  </si>
+  <si>
+    <t>Gulliver hajóorvos fantasztikus országokban (Liliput, Brobdingnag, Laputa, Nyihahák országa) tesz utazásokat, ahol társadalmukon keresztül egyre élesebb kritikát fogalmaz meg a világról.</t>
+  </si>
+  <si>
+    <t>Az angol társadalom, a politika és az egész emberi nem kíméletlen, keserű szatírája. A méretbeli és logikai torzításokkal az emberi lét relativitását és bűnösségét hangsúlyozza.</t>
+  </si>
+  <si>
+    <t>Voltaire</t>
+  </si>
+  <si>
+    <t>Candide vagy az optimizmus</t>
+  </si>
+  <si>
+    <t>Tézisregény / Pikareszk</t>
+  </si>
+  <si>
+    <t>Francia felvilágosodás (1759)</t>
+  </si>
+  <si>
+    <t>Candide elindul a nagyvilágba, hogy próbára tegye mestere, Pangloss elméletét a "legjobb világról". Útját folyamatos háborúk, kínzások és természeti katasztrófák kísérik.</t>
+  </si>
+  <si>
+    <t>Leibniz túlzottan optimista filozófiájának metsző gúnyirata. Befejezése az elvont tézisek helyett egy nagyon is gyakorlatias tanulsággal zárul: világmegváltó viták helyett "műveljük a kertünket".</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,7 +820,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -176,12 +828,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,177 +1141,919 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="120" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="216.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="119.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="206.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F12" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="13" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
+      <c r="B16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
